--- a/public/templates/importacao-cobrancas.xlsx
+++ b/public/templates/importacao-cobrancas.xlsx
@@ -214,27 +214,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaDados" displayName="TabelaDados" ref="A1:M50" headerRowCount="1">
-  <tableColumns count="13">
-    <tableColumn id="1" name="condominio_cnpj"/>
-    <tableColumn id="2" name="unidade"/>
-    <tableColumn id="3" name="bloco"/>
-    <tableColumn id="4" name="responsavel_nome"/>
-    <tableColumn id="5" name="responsavel_documento"/>
-    <tableColumn id="6" name="telefone"/>
-    <tableColumn id="7" name="email"/>
-    <tableColumn id="8" name="competencia"/>
-    <tableColumn id="9" name="vencimento"/>
-    <tableColumn id="10" name="valor_original"/>
-    <tableColumn id="11" name="valor_atualizado"/>
-    <tableColumn id="12" name="status"/>
-    <tableColumn id="13" name="observacoes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -3662,9 +3641,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
